--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130134250</v>
+        <v>137550816</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>90917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1593</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750614</v>
+        <v>750468</v>
       </c>
       <c r="R2" t="n">
-        <v>7110958</v>
+        <v>7111113</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,53 +775,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134250</t>
+          <t>https://artportalen.se/Sighting/137550816</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130134265</v>
+        <v>137550823</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>91193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750588</v>
+        <v>750545</v>
       </c>
       <c r="R3" t="n">
-        <v>7111098</v>
+        <v>7111137</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,53 +887,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134265</t>
+          <t>https://artportalen.se/Sighting/137550823</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130134269</v>
+        <v>137550815</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>92152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750667</v>
+        <v>750468</v>
       </c>
       <c r="R4" t="n">
-        <v>7111133</v>
+        <v>7111101</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,53 +999,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134269</t>
+          <t>https://artportalen.se/Sighting/137550815</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130134270</v>
+        <v>137550772</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>93527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750644</v>
+        <v>750466</v>
       </c>
       <c r="R5" t="n">
-        <v>7111054</v>
+        <v>7111141</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,53 +1111,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134270</t>
+          <t>https://artportalen.se/Sighting/137550772</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130134271</v>
+        <v>137550774</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>93527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750620</v>
+        <v>750478</v>
       </c>
       <c r="R6" t="n">
-        <v>7111033</v>
+        <v>7111130</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,12 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,53 +1223,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134271</t>
+          <t>https://artportalen.se/Sighting/137550774</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130134238</v>
+        <v>137550820</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>93527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750467</v>
+        <v>750530</v>
       </c>
       <c r="R7" t="n">
-        <v>7110939</v>
+        <v>7111117</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,31 +1335,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134238</t>
+          <t>https://artportalen.se/Sighting/137550820</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130134267</v>
+        <v>130134250</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750666</v>
+        <v>750614</v>
       </c>
       <c r="R8" t="n">
-        <v>7111136</v>
+        <v>7110958</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,38 +1452,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134267</t>
+          <t>https://artportalen.se/Sighting/130134250</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130134353</v>
+        <v>130134265</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750686</v>
+        <v>750588</v>
       </c>
       <c r="R9" t="n">
-        <v>7111300</v>
+        <v>7111098</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,12 +1523,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,7 +1548,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1522,38 +1558,38 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134353</t>
+          <t>https://artportalen.se/Sighting/130134265</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130134356</v>
+        <v>130134269</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750732</v>
+        <v>750667</v>
       </c>
       <c r="R10" t="n">
-        <v>7111314</v>
+        <v>7111133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1629,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,7 +1654,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1628,38 +1664,38 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134356</t>
+          <t>https://artportalen.se/Sighting/130134269</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130134351</v>
+        <v>130134270</v>
       </c>
       <c r="B11" t="n">
-        <v>93209</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750716</v>
+        <v>750644</v>
       </c>
       <c r="R11" t="n">
-        <v>7111284</v>
+        <v>7111054</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,12 +1735,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,7 +1760,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1734,38 +1770,38 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134351</t>
+          <t>https://artportalen.se/Sighting/130134270</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130134354</v>
+        <v>130134271</v>
       </c>
       <c r="B12" t="n">
-        <v>93235</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750685</v>
+        <v>750620</v>
       </c>
       <c r="R12" t="n">
-        <v>7111314</v>
+        <v>7111033</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,12 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,7 +1866,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1840,38 +1876,38 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134354</t>
+          <t>https://artportalen.se/Sighting/130134271</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130134355</v>
+        <v>137550770</v>
       </c>
       <c r="B13" t="n">
-        <v>93235</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,13 +1917,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750714</v>
+        <v>750405</v>
       </c>
       <c r="R13" t="n">
-        <v>7111325</v>
+        <v>7111067</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1911,12 +1947,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,31 +1977,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134355</t>
+          <t>https://artportalen.se/Sighting/137550770</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130134261</v>
+        <v>137550784</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1987,13 +2029,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750701</v>
+        <v>750632</v>
       </c>
       <c r="R14" t="n">
-        <v>7111370</v>
+        <v>7111103</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,12 +2059,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2037,31 +2089,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134261</t>
+          <t>https://artportalen.se/Sighting/137550784</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130134262</v>
+        <v>137550785</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,13 +2141,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750629</v>
+        <v>750542</v>
       </c>
       <c r="R15" t="n">
-        <v>7111290</v>
+        <v>7111035</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2123,12 +2171,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,31 +2201,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134262</t>
+          <t>https://artportalen.se/Sighting/137550785</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130134263</v>
+        <v>137550813</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,13 +2253,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750665</v>
+        <v>750468</v>
       </c>
       <c r="R16" t="n">
-        <v>7111235</v>
+        <v>7111080</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2229,12 +2283,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2249,53 +2313,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134263</t>
+          <t>https://artportalen.se/Sighting/137550813</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130134258</v>
+        <v>137550818</v>
       </c>
       <c r="B17" t="n">
-        <v>78730</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,13 +2365,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750733</v>
+        <v>750483</v>
       </c>
       <c r="R17" t="n">
-        <v>7111297</v>
+        <v>7111103</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2335,12 +2395,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,53 +2425,49 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134258</t>
+          <t>https://artportalen.se/Sighting/137550818</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130134260</v>
+        <v>137550819</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,13 +2477,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750719</v>
+        <v>750500</v>
       </c>
       <c r="R18" t="n">
-        <v>7111349</v>
+        <v>7111120</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,12 +2507,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2461,76 +2537,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130134260</t>
+          <t>https://artportalen.se/Sighting/137550819</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129574107</v>
+        <v>137550822</v>
       </c>
       <c r="B19" t="n">
-        <v>57141</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kälen, Vb</t>
+          <t>Huggberget, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750675</v>
+        <v>750536</v>
       </c>
       <c r="R19" t="n">
-        <v>7111322</v>
+        <v>7111092</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2554,22 +2619,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,70 +2649,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129574107</t>
+          <t>https://artportalen.se/Sighting/137550822</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130134257</v>
+        <v>137550825</v>
       </c>
       <c r="B20" t="n">
-        <v>8444</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Huggberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750740</v>
+        <v>750546</v>
       </c>
       <c r="R20" t="n">
-        <v>7111322</v>
+        <v>7111141</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,12 +2731,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2691,20 +2761,4567 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550825</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137550846</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>750650</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7111121</v>
+      </c>
+      <c r="S21" t="n">
+        <v>7</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550846</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137550848</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>750637</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7111092</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550848</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137550849</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>750590</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7111061</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550849</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137550851</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>750545</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7110980</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550851</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137550854</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>750517</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7110980</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550854</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137550766</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>750428</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7110916</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550766</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137550783</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>750640</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7111110</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550783</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130134238</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>750467</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7110939</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Sofia Lundman</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Lisa Sandberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
+      <c r="AY28" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134238</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130134267</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>750666</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7111136</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134267</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137550852</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>750516</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7110985</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550852</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137550768</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98300</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>750435</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7110924</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550768</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137550782</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79571</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>185</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>750665</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7111270</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550782</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137550780</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93023</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>750649</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7111223</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Björkstubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Björkstubbe</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550780</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130134353</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>750686</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7111300</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134353</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130134356</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>750732</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7111314</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134356</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130134351</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>750716</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7111284</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134351</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137550832</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92152</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>750666</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7111315</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550832</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130134354</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>750685</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7111314</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134354</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130134355</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>750714</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7111325</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134355</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137550776</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93527</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>750493</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7111170</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550776</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137550777</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93527</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>750533</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7111177</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550777</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137550837</v>
+      </c>
+      <c r="B42" t="n">
+        <v>93527</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>750677</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7111317</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550837</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137550840</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93527</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>750693</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7111298</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550840</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137550842</v>
+      </c>
+      <c r="B44" t="n">
+        <v>93527</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>750697</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7111284</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550842</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137550843</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93527</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>750685</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7111271</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550843</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130134261</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>750701</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7111370</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134261</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130134262</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>750629</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7111290</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134262</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130134263</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>750665</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7111235</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134263</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137550778</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>750551</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7111192</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550778</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137550779</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>750649</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7111221</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550779</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137550781</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>750679</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7111305</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550781</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137550827</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>750629</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7111193</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550827</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137550829</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>750653</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7111247</v>
+      </c>
+      <c r="S53" t="n">
+        <v>7</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550829</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137550836</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>750665</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7111328</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550836</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137550839</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>750681</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7111296</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550839</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137550845</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>750653</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7111195</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550845</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137550830</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79563</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>750626</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7111303</v>
+      </c>
+      <c r="S57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137550830</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130134258</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>750733</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7111297</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134258</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130134260</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>750719</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7111349</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134260</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129574107</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>750675</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7111322</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574107</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130134257</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>750740</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7111322</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130134257</t>
         </is>
@@ -2731,6 +7348,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
